--- a/copilot-vs-claude-compare-start.xlsx
+++ b/copilot-vs-claude-compare-start.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29911"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29909"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\copilot-opus-vs-claude-excel-addin\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GeorgeMount\Documents\GitHub\copilot-opus-vs-claude-excel-addin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC85ACE6-32EF-49B1-BF68-48C992BEA631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56B505B3-7BAE-46FC-AC8A-06D00CF64E28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" xr2:uid="{7247F7D7-E9B5-47F9-BB86-9254210419BD}"/>
+    <workbookView xWindow="-23136" yWindow="-96" windowWidth="23232" windowHeight="13152" activeTab="2" xr2:uid="{7247F7D7-E9B5-47F9-BB86-9254210419BD}"/>
   </bookViews>
   <sheets>
     <sheet name="data-copilot" sheetId="2" r:id="rId1"/>
     <sheet name="data-claude" sheetId="3" r:id="rId2"/>
-    <sheet name="Prompt 1" sheetId="1" r:id="rId3"/>
+    <sheet name="Prompt" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -977,7 +977,7 @@
     <col min="7" max="7" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="48" x14ac:dyDescent="0.85">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.85">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="1:7" ht="48" x14ac:dyDescent="0.85">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.85">
       <c r="A5" s="3">
         <v>46026</v>
       </c>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="G5" s="4"/>
     </row>
-    <row r="6" spans="1:7" ht="48" x14ac:dyDescent="0.85">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.85">
       <c r="A6" s="3">
         <v>46027</v>
       </c>
@@ -1543,7 +1543,7 @@
     <col min="7" max="7" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="48" x14ac:dyDescent="0.85">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.85">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="1:7" ht="48" x14ac:dyDescent="0.85">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.85">
       <c r="A5" s="3">
         <v>46026</v>
       </c>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="G5" s="4"/>
     </row>
-    <row r="6" spans="1:7" ht="48" x14ac:dyDescent="0.85">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.85">
       <c r="A6" s="3">
         <v>46027</v>
       </c>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="G12" s="4"/>
     </row>
-    <row r="13" spans="1:7" ht="48" x14ac:dyDescent="0.85">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.85">
       <c r="A13" s="3">
         <v>46029</v>
       </c>
